--- a/W2_sdm_coef.xlsx
+++ b/W2_sdm_coef.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>变量</t>
   </si>
@@ -29,6 +29,15 @@
   </si>
   <si>
     <t>p值</t>
+  </si>
+  <si>
+    <t>稳健标准误(线性部分)</t>
+  </si>
+  <si>
+    <t>稳健z值(线性部分)</t>
+  </si>
+  <si>
+    <t>稳健p值(线性部分)</t>
   </si>
   <si>
     <t>rho</t>
@@ -422,10 +431,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,206 +450,305 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>0.5358366815739438</v>
+        <v>0.5077680930389624</v>
       </c>
       <c r="C2">
-        <v>0.1276946311031464</v>
+        <v>0.1173767831930165</v>
       </c>
       <c r="D2">
-        <v>4.196235009607549</v>
+        <v>4.325967020275035</v>
       </c>
       <c r="E2">
-        <v>2.713886492200501E-05</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>1.518641447129099E-05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>0.008607485047028112</v>
+        <v>-0.006822766513401072</v>
       </c>
       <c r="C3">
-        <v>0.0385015211834892</v>
+        <v>0.03422732970017264</v>
       </c>
       <c r="D3">
-        <v>0.2235622069581839</v>
+        <v>-0.1993368040442447</v>
       </c>
       <c r="E3">
-        <v>0.823097973803967</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>0.8419992913500076</v>
+      </c>
+      <c r="F3">
+        <v>0.0238019060186433</v>
+      </c>
+      <c r="G3">
+        <v>-0.2866479057625472</v>
+      </c>
+      <c r="H3">
+        <v>0.7743819294364906</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>-1.560373803816342</v>
+        <v>-1.424596472780192</v>
       </c>
       <c r="C4">
-        <v>0.4446192252390895</v>
+        <v>0.364774690254835</v>
       </c>
       <c r="D4">
-        <v>-3.50946093925036</v>
+        <v>-3.905414796692599</v>
       </c>
       <c r="E4">
-        <v>0.0004490160060564019</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>9.406389721622332E-05</v>
+      </c>
+      <c r="F4">
+        <v>0.3680907940505119</v>
+      </c>
+      <c r="G4">
+        <v>-3.870231192428842</v>
+      </c>
+      <c r="H4">
+        <v>0.0001087321895740789</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>0.1539341909226618</v>
+        <v>0.1094796744353908</v>
       </c>
       <c r="C5">
-        <v>0.04094325094514714</v>
+        <v>0.02287272858043501</v>
       </c>
       <c r="D5">
-        <v>3.759696344799095</v>
+        <v>4.78647197908159</v>
       </c>
       <c r="E5">
-        <v>0.0001701197181249725</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1.697386247556665E-06</v>
+      </c>
+      <c r="F5">
+        <v>0.019008129726767</v>
+      </c>
+      <c r="G5">
+        <v>5.759623698339084</v>
+      </c>
+      <c r="H5">
+        <v>8.430166120731997E-09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>3.571451136657932</v>
+        <v>2.360131542269178</v>
       </c>
       <c r="C6">
-        <v>2.153317973483191</v>
+        <v>1.718155152180702</v>
       </c>
       <c r="D6">
-        <v>1.658580470064428</v>
+        <v>1.373642851330202</v>
       </c>
       <c r="E6">
-        <v>0.09720035988623055</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>0.169552586773255</v>
+      </c>
+      <c r="F6">
+        <v>1.836026708052082</v>
+      </c>
+      <c r="G6">
+        <v>1.285455996864632</v>
+      </c>
+      <c r="H6">
+        <v>0.1986329840515904</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>66.96509524580102</v>
+        <v>75.79552121217607</v>
       </c>
       <c r="C7">
-        <v>25.20140223081519</v>
+        <v>21.53719326442912</v>
       </c>
       <c r="D7">
-        <v>2.657197192143498</v>
+        <v>3.519285000676488</v>
       </c>
       <c r="E7">
-        <v>0.007879333966567703</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>0.0004327115979172458</v>
+      </c>
+      <c r="F7">
+        <v>20.84629168883997</v>
+      </c>
+      <c r="G7">
+        <v>3.635923469916383</v>
+      </c>
+      <c r="H7">
+        <v>0.0002769865617828771</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>-0.05370965565094452</v>
+        <v>-0.03733863536070976</v>
       </c>
       <c r="C8">
-        <v>0.1617405236420799</v>
+        <v>0.142477686580371</v>
       </c>
       <c r="D8">
-        <v>-0.332072967500712</v>
+        <v>-0.2620665470985676</v>
       </c>
       <c r="E8">
-        <v>0.7398341618187474</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>0.7932701372063398</v>
+      </c>
+      <c r="F8">
+        <v>0.1191644404986598</v>
+      </c>
+      <c r="G8">
+        <v>-0.3133370593145167</v>
+      </c>
+      <c r="H8">
+        <v>0.7540245974102833</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>-0.8448321101851202</v>
+        <v>0.3800157913465226</v>
       </c>
       <c r="C9">
-        <v>1.318893959543774</v>
+        <v>1.118086461131496</v>
       </c>
       <c r="D9">
-        <v>-0.6405610580530376</v>
+        <v>0.339880505271434</v>
       </c>
       <c r="E9">
-        <v>0.5218079072830717</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>0.733946518167685</v>
+      </c>
+      <c r="F9">
+        <v>1.215708313538698</v>
+      </c>
+      <c r="G9">
+        <v>0.3125879679479762</v>
+      </c>
+      <c r="H9">
+        <v>0.7545937205469249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>0.1530336566835987</v>
+        <v>0.1193998499741868</v>
       </c>
       <c r="C10">
-        <v>0.1476147074148175</v>
+        <v>0.0839297430878375</v>
       </c>
       <c r="D10">
-        <v>1.036710090503064</v>
+        <v>1.422616650324161</v>
       </c>
       <c r="E10">
-        <v>0.2998709879648382</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>0.1548473145656737</v>
+      </c>
+      <c r="F10">
+        <v>0.05912289798180544</v>
+      </c>
+      <c r="G10">
+        <v>2.019519577861882</v>
+      </c>
+      <c r="H10">
+        <v>0.0434332445421981</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>6.851515423681622</v>
+        <v>4.9873858939797</v>
       </c>
       <c r="C11">
-        <v>9.663518106551948</v>
+        <v>7.757822326394849</v>
       </c>
       <c r="D11">
-        <v>0.7090083909540394</v>
+        <v>0.6428847792776657</v>
       </c>
       <c r="E11">
-        <v>0.4783192697603091</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>0.5202988664491615</v>
+      </c>
+      <c r="F11">
+        <v>7.967795848211432</v>
+      </c>
+      <c r="G11">
+        <v>0.6259429820982727</v>
+      </c>
+      <c r="H11">
+        <v>0.5313523406944531</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>450.3834406807757</v>
+        <v>415.2752421015188</v>
       </c>
       <c r="C12">
-        <v>116.1883954170024</v>
+        <v>94.39194168083309</v>
       </c>
       <c r="D12">
-        <v>3.876320342185127</v>
+        <v>4.399477695942377</v>
       </c>
       <c r="E12">
-        <v>0.0001060480467456326</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>1.085117288424087E-05</v>
+      </c>
+      <c r="F12">
+        <v>97.75835195861825</v>
+      </c>
+      <c r="G12">
+        <v>4.247977116853479</v>
+      </c>
+      <c r="H12">
+        <v>2.157094213828259E-05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>-3.17313895089158</v>
+        <v>-3.266590603080405</v>
       </c>
       <c r="C13">
-        <v>0.1390995278697683</v>
+        <v>0.121628144894839</v>
       </c>
       <c r="D13">
-        <v>-22.81200374642843</v>
+        <v>-26.85719334044544</v>
       </c>
       <c r="E13">
         <v>0</v>
